--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260224_202304.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260224_202304.xlsx
@@ -5552,7 +5552,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260224_202304.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260224_202304.xlsx
@@ -5552,7 +5552,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
